--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD90C406-87E4-DA45-A71C-AC601F3A8992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0413E1AE-7A84-3848-9620-27958F4BB945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20760" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E909"/>
+  <dimension ref="A1:E910"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -23585,7 +23585,7 @@
         <v>0.50347222222222221</v>
       </c>
       <c r="D909" s="7" t="str">
-        <f t="shared" ref="D909" si="22">IF(
+        <f t="shared" ref="D909:D910" si="22">IF(
  AND(
   A909 &gt;= IF(
          YEAR(A909)&gt;=2007,
@@ -23605,6 +23605,24 @@
       </c>
       <c r="E909" s="20">
         <v>543212</v>
+      </c>
+    </row>
+    <row r="910" spans="1:5" ht="16">
+      <c r="A910" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B910" s="8">
+        <v>46274</v>
+      </c>
+      <c r="C910" s="21">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="D910" s="7" t="str">
+        <f t="shared" si="22"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E910" s="20">
+        <v>533545</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0413E1AE-7A84-3848-9620-27958F4BB945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CE9285-05D8-D441-93BB-B215EB0298C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20760" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E910"/>
+  <dimension ref="A1:E911"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -23585,7 +23585,7 @@
         <v>0.50347222222222221</v>
       </c>
       <c r="D909" s="7" t="str">
-        <f t="shared" ref="D909:D910" si="22">IF(
+        <f t="shared" ref="D909:D911" si="22">IF(
  AND(
   A909 &gt;= IF(
          YEAR(A909)&gt;=2007,
@@ -23623,6 +23623,24 @@
       </c>
       <c r="E910" s="20">
         <v>533545</v>
+      </c>
+    </row>
+    <row r="911" spans="1:5" ht="16">
+      <c r="A911" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B911" s="8">
+        <v>46281</v>
+      </c>
+      <c r="C911" s="21">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="D911" s="7" t="str">
+        <f t="shared" si="22"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E911" s="20">
+        <v>494865</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/US Rail Traffic.xlsx
+++ b/data_lake/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CE9285-05D8-D441-93BB-B215EB0298C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51031673-94CA-7844-8B9D-558F8E67A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20760" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E911"/>
+  <dimension ref="A1:E912"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -23641,6 +23641,36 @@
       </c>
       <c r="E911" s="20">
         <v>494865</v>
+      </c>
+    </row>
+    <row r="912" spans="1:5" ht="16">
+      <c r="A912" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B912" s="8">
+        <v>46288</v>
+      </c>
+      <c r="C912" s="21">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="D912" s="7" t="str">
+        <f t="shared" ref="D912" si="23">IF(
+ AND(
+  A912 &gt;= IF(
+         YEAR(A912)&gt;=2007,
+         DATE(YEAR(A912),3,14)-WEEKDAY(DATE(YEAR(A912),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A912),4,7)-WEEKDAY(DATE(YEAR(A912),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A912 &lt;  IF(
+         YEAR(A912)&gt;=2007,
+         DATE(YEAR(A912),11,7)-WEEKDAY(DATE(YEAR(A912),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A912),10,31)-WEEKDAY(DATE(YEAR(A912),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
